--- a/Reseförslag/Resplan Indien CP & ESS 2027.xlsx
+++ b/Reseförslag/Resplan Indien CP & ESS 2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CPS-Local\Resor\Indien 2027\Reseförslag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E6ADAB-0B8D-4900-ACF5-E1FCDFA879DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93367088-6E13-4AC9-A391-F814E6FFD2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6945" yWindow="2010" windowWidth="21600" windowHeight="11295" xr2:uid="{D761A4C5-6C5D-4467-9BFE-AE848DE17E5E}"/>
+    <workbookView xWindow="-105" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{D761A4C5-6C5D-4467-9BFE-AE848DE17E5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resplan" sheetId="2" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <t>Delningsfaktor</t>
   </si>
   <si>
-    <t>21 d</t>
-  </si>
-  <si>
     <t>/en</t>
   </si>
   <si>
@@ -262,6 +259,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Flygplatsmat / pers:</t>
   </si>
 </sst>
 </file>
@@ -338,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -368,6 +368,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,7 +721,7 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -828,19 +831,19 @@
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="T2" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:38" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="15">
         <v>46395</v>
@@ -950,33 +953,33 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>65</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -993,30 +996,30 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S8" s="16"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T10" s="16"/>
       <c r="U10" s="16"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL11" t="s">
         <v>72</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E755E-4DE9-4945-B96D-BB45CDEF6EB6}">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1078,7 +1081,7 @@
         <v>55</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -3043,12 +3046,26 @@
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N45" t="s">
-        <v>56</v>
+      <c r="O45" s="20" t="s">
+        <v>73</v>
       </c>
       <c r="P45">
-        <f>P44/21</f>
-        <v>375.6016952380952</v>
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P46">
+        <f>P44+P45</f>
+        <v>7287.6355999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N47">
+        <v>18</v>
+      </c>
+      <c r="P47">
+        <f>P46/N47</f>
+        <v>404.86864444444444</v>
       </c>
     </row>
   </sheetData>
